--- a/public/plantilla-materiales.xlsx
+++ b/public/plantilla-materiales.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de Materiales" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,10 +16,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -103,6 +103,17 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -299,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -319,47 +330,47 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -407,17 +418,17 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -430,7 +441,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -445,13 +456,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -481,10 +492,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -502,13 +513,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -518,7 +529,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -531,6 +542,49 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -902,7 +956,9 @@
     <col width="14" customWidth="1" style="34" min="7" max="7"/>
     <col width="20.77734375" customWidth="1" style="34" min="8" max="8"/>
     <col width="14" customWidth="1" style="34" min="9" max="10"/>
+    <col width="13" customWidth="1" style="34" min="10" max="10"/>
     <col width="12" customWidth="1" style="34" min="11" max="12"/>
+    <col width="13" customWidth="1" style="34" min="12" max="12"/>
     <col width="20.77734375" customWidth="1" style="34" min="13" max="13"/>
     <col width="25.77734375" customWidth="1" style="34" min="14" max="14"/>
   </cols>
@@ -1043,10 +1099,10 @@
       </c>
       <c r="B10" s="90" t="n"/>
       <c r="C10" s="84" t="n"/>
-      <c r="D10" s="24" t="n"/>
-      <c r="E10" s="90" t="n"/>
-      <c r="F10" s="90" t="n"/>
-      <c r="G10" s="84" t="n"/>
+      <c r="D10" s="91" t="n"/>
+      <c r="E10" s="92" t="n"/>
+      <c r="F10" s="92" t="n"/>
+      <c r="G10" s="93" t="n"/>
       <c r="H10" s="22" t="inlineStr">
         <is>
           <t>Tipo de proyecto</t>
@@ -1054,10 +1110,10 @@
       </c>
       <c r="I10" s="90" t="n"/>
       <c r="J10" s="84" t="n"/>
-      <c r="K10" s="24" t="n"/>
-      <c r="L10" s="90" t="n"/>
-      <c r="M10" s="90" t="n"/>
-      <c r="N10" s="84" t="n"/>
+      <c r="K10" s="91" t="n"/>
+      <c r="L10" s="92" t="n"/>
+      <c r="M10" s="92" t="n"/>
+      <c r="N10" s="93" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="34">
       <c r="A11" s="22" t="inlineStr">
@@ -1067,10 +1123,10 @@
       </c>
       <c r="B11" s="90" t="n"/>
       <c r="C11" s="84" t="n"/>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="90" t="n"/>
-      <c r="F11" s="90" t="n"/>
-      <c r="G11" s="84" t="n"/>
+      <c r="D11" s="91" t="n"/>
+      <c r="E11" s="92" t="n"/>
+      <c r="F11" s="92" t="n"/>
+      <c r="G11" s="93" t="n"/>
       <c r="H11" s="22" t="inlineStr">
         <is>
           <t>Contratante</t>
@@ -1078,10 +1134,10 @@
       </c>
       <c r="I11" s="90" t="n"/>
       <c r="J11" s="84" t="n"/>
-      <c r="K11" s="24" t="n"/>
-      <c r="L11" s="90" t="n"/>
-      <c r="M11" s="90" t="n"/>
-      <c r="N11" s="84" t="n"/>
+      <c r="K11" s="91" t="n"/>
+      <c r="L11" s="92" t="n"/>
+      <c r="M11" s="92" t="n"/>
+      <c r="N11" s="93" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="34">
       <c r="A12" s="22" t="inlineStr">
@@ -1091,10 +1147,10 @@
       </c>
       <c r="B12" s="90" t="n"/>
       <c r="C12" s="84" t="n"/>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="90" t="n"/>
-      <c r="F12" s="90" t="n"/>
-      <c r="G12" s="84" t="n"/>
+      <c r="D12" s="91" t="n"/>
+      <c r="E12" s="92" t="n"/>
+      <c r="F12" s="92" t="n"/>
+      <c r="G12" s="93" t="n"/>
       <c r="H12" s="22" t="inlineStr">
         <is>
           <t>Responsable del control</t>
@@ -1102,10 +1158,10 @@
       </c>
       <c r="I12" s="90" t="n"/>
       <c r="J12" s="84" t="n"/>
-      <c r="K12" s="24" t="n"/>
-      <c r="L12" s="90" t="n"/>
-      <c r="M12" s="90" t="n"/>
-      <c r="N12" s="84" t="n"/>
+      <c r="K12" s="91" t="n"/>
+      <c r="L12" s="92" t="n"/>
+      <c r="M12" s="92" t="n"/>
+      <c r="N12" s="93" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="34">
       <c r="A13" s="40" t="inlineStr">
@@ -1200,30 +1256,30 @@
       </c>
     </row>
     <row r="15" ht="22.05" customHeight="1" s="34">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="24" t="n"/>
-      <c r="C15" s="24" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="20" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="20" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="20" t="n"/>
+      <c r="B15" s="91" t="n"/>
+      <c r="C15" s="91" t="n"/>
+      <c r="D15" s="95" t="n"/>
+      <c r="E15" s="96" t="n"/>
+      <c r="F15" s="97" t="n"/>
+      <c r="G15" s="96" t="n"/>
+      <c r="H15" s="97" t="n"/>
+      <c r="I15" s="96" t="n"/>
       <c r="J15" s="77">
         <f>IF(G15="","",G15-N(I15))</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="98">
         <f>IF(OR(E15="",E15=0,G15=""),"",G15/E15)</f>
         <v/>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="98">
         <f>IF(OR(F15="",F15=0,H15=""),"",H15/F15-1)</f>
         <v/>
       </c>
-      <c r="M15" s="8">
+      <c r="M15" s="99">
         <f>IF(OR(G15="",F15="",H15=""),"",G15*(H15-F15))</f>
         <v/>
       </c>
@@ -1233,30 +1289,30 @@
       </c>
     </row>
     <row r="16" ht="22.05" customHeight="1" s="34">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="24" t="n"/>
-      <c r="C16" s="24" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="20" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="20" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="20" t="n"/>
+      <c r="B16" s="91" t="n"/>
+      <c r="C16" s="91" t="n"/>
+      <c r="D16" s="95" t="n"/>
+      <c r="E16" s="96" t="n"/>
+      <c r="F16" s="97" t="n"/>
+      <c r="G16" s="96" t="n"/>
+      <c r="H16" s="97" t="n"/>
+      <c r="I16" s="96" t="n"/>
       <c r="J16" s="77">
         <f>IF(G16="","",G16-N(I16))</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="98">
         <f>IF(OR(E16="",E16=0,G16=""),"",G16/E16)</f>
         <v/>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="98">
         <f>IF(OR(F16="",F16=0,H16=""),"",H16/F16-1)</f>
         <v/>
       </c>
-      <c r="M16" s="8">
+      <c r="M16" s="99">
         <f>IF(OR(G16="",F16="",H16=""),"",G16*(H16-F16))</f>
         <v/>
       </c>
@@ -1266,30 +1322,30 @@
       </c>
     </row>
     <row r="17" ht="22.05" customHeight="1" s="34">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="94" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="24" t="n"/>
-      <c r="C17" s="24" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="20" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="20" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="20" t="n"/>
+      <c r="B17" s="91" t="n"/>
+      <c r="C17" s="91" t="n"/>
+      <c r="D17" s="95" t="n"/>
+      <c r="E17" s="96" t="n"/>
+      <c r="F17" s="97" t="n"/>
+      <c r="G17" s="96" t="n"/>
+      <c r="H17" s="97" t="n"/>
+      <c r="I17" s="96" t="n"/>
       <c r="J17" s="77">
         <f>IF(G17="","",G17-N(I17))</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="98">
         <f>IF(OR(E17="",E17=0,G17=""),"",G17/E17)</f>
         <v/>
       </c>
-      <c r="L17" s="16">
+      <c r="L17" s="98">
         <f>IF(OR(F17="",F17=0,H17=""),"",H17/F17-1)</f>
         <v/>
       </c>
-      <c r="M17" s="8">
+      <c r="M17" s="99">
         <f>IF(OR(G17="",F17="",H17=""),"",G17*(H17-F17))</f>
         <v/>
       </c>
@@ -1299,30 +1355,30 @@
       </c>
     </row>
     <row r="18" ht="22.05" customHeight="1" s="34">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="24" t="n"/>
-      <c r="C18" s="24" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="20" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="20" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="20" t="n"/>
+      <c r="B18" s="91" t="n"/>
+      <c r="C18" s="91" t="n"/>
+      <c r="D18" s="95" t="n"/>
+      <c r="E18" s="96" t="n"/>
+      <c r="F18" s="97" t="n"/>
+      <c r="G18" s="96" t="n"/>
+      <c r="H18" s="97" t="n"/>
+      <c r="I18" s="96" t="n"/>
       <c r="J18" s="77">
         <f>IF(G18="","",G18-N(I18))</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="98">
         <f>IF(OR(E18="",E18=0,G18=""),"",G18/E18)</f>
         <v/>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="98">
         <f>IF(OR(F18="",F18=0,H18=""),"",H18/F18-1)</f>
         <v/>
       </c>
-      <c r="M18" s="8">
+      <c r="M18" s="99">
         <f>IF(OR(G18="",F18="",H18=""),"",G18*(H18-F18))</f>
         <v/>
       </c>
@@ -1332,30 +1388,30 @@
       </c>
     </row>
     <row r="19" ht="22.05" customHeight="1" s="34">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="94" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="24" t="n"/>
-      <c r="C19" s="24" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="20" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="20" t="n"/>
+      <c r="B19" s="91" t="n"/>
+      <c r="C19" s="91" t="n"/>
+      <c r="D19" s="95" t="n"/>
+      <c r="E19" s="96" t="n"/>
+      <c r="F19" s="97" t="n"/>
+      <c r="G19" s="96" t="n"/>
+      <c r="H19" s="97" t="n"/>
+      <c r="I19" s="96" t="n"/>
       <c r="J19" s="77">
         <f>IF(G19="","",G19-N(I19))</f>
         <v/>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="98">
         <f>IF(OR(E19="",E19=0,G19=""),"",G19/E19)</f>
         <v/>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="98">
         <f>IF(OR(F19="",F19=0,H19=""),"",H19/F19-1)</f>
         <v/>
       </c>
-      <c r="M19" s="8">
+      <c r="M19" s="99">
         <f>IF(OR(G19="",F19="",H19=""),"",G19*(H19-F19))</f>
         <v/>
       </c>
@@ -1365,30 +1421,30 @@
       </c>
     </row>
     <row r="20" ht="22.05" customHeight="1" s="34">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="24" t="n"/>
-      <c r="C20" s="24" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="20" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="20" t="n"/>
+      <c r="B20" s="91" t="n"/>
+      <c r="C20" s="91" t="n"/>
+      <c r="D20" s="95" t="n"/>
+      <c r="E20" s="96" t="n"/>
+      <c r="F20" s="97" t="n"/>
+      <c r="G20" s="96" t="n"/>
+      <c r="H20" s="97" t="n"/>
+      <c r="I20" s="96" t="n"/>
       <c r="J20" s="77">
         <f>IF(G20="","",G20-N(I20))</f>
         <v/>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="98">
         <f>IF(OR(E20="",E20=0,G20=""),"",G20/E20)</f>
         <v/>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="98">
         <f>IF(OR(F20="",F20=0,H20=""),"",H20/F20-1)</f>
         <v/>
       </c>
-      <c r="M20" s="8">
+      <c r="M20" s="99">
         <f>IF(OR(G20="",F20="",H20=""),"",G20*(H20-F20))</f>
         <v/>
       </c>
@@ -1398,30 +1454,30 @@
       </c>
     </row>
     <row r="21" ht="22.05" customHeight="1" s="34">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="94" t="n">
         <v>7</v>
       </c>
-      <c r="B21" s="24" t="n"/>
-      <c r="C21" s="24" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="20" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="20" t="n"/>
+      <c r="B21" s="91" t="n"/>
+      <c r="C21" s="91" t="n"/>
+      <c r="D21" s="95" t="n"/>
+      <c r="E21" s="96" t="n"/>
+      <c r="F21" s="97" t="n"/>
+      <c r="G21" s="96" t="n"/>
+      <c r="H21" s="97" t="n"/>
+      <c r="I21" s="96" t="n"/>
       <c r="J21" s="77">
         <f>IF(G21="","",G21-N(I21))</f>
         <v/>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="98">
         <f>IF(OR(E21="",E21=0,G21=""),"",G21/E21)</f>
         <v/>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="98">
         <f>IF(OR(F21="",F21=0,H21=""),"",H21/F21-1)</f>
         <v/>
       </c>
-      <c r="M21" s="8">
+      <c r="M21" s="99">
         <f>IF(OR(G21="",F21="",H21=""),"",G21*(H21-F21))</f>
         <v/>
       </c>
@@ -1431,30 +1487,30 @@
       </c>
     </row>
     <row r="22" ht="22.05" customHeight="1" s="34">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="94" t="n">
         <v>8</v>
       </c>
-      <c r="B22" s="24" t="n"/>
-      <c r="C22" s="24" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="20" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="20" t="n"/>
+      <c r="B22" s="91" t="n"/>
+      <c r="C22" s="91" t="n"/>
+      <c r="D22" s="95" t="n"/>
+      <c r="E22" s="96" t="n"/>
+      <c r="F22" s="97" t="n"/>
+      <c r="G22" s="96" t="n"/>
+      <c r="H22" s="97" t="n"/>
+      <c r="I22" s="96" t="n"/>
       <c r="J22" s="77">
         <f>IF(G22="","",G22-N(I22))</f>
         <v/>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="98">
         <f>IF(OR(E22="",E22=0,G22=""),"",G22/E22)</f>
         <v/>
       </c>
-      <c r="L22" s="16">
+      <c r="L22" s="98">
         <f>IF(OR(F22="",F22=0,H22=""),"",H22/F22-1)</f>
         <v/>
       </c>
-      <c r="M22" s="8">
+      <c r="M22" s="99">
         <f>IF(OR(G22="",F22="",H22=""),"",G22*(H22-F22))</f>
         <v/>
       </c>
@@ -1464,30 +1520,30 @@
       </c>
     </row>
     <row r="23" ht="22.05" customHeight="1" s="34">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="94" t="n">
         <v>9</v>
       </c>
-      <c r="B23" s="24" t="n"/>
-      <c r="C23" s="24" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="20" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="20" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="20" t="n"/>
+      <c r="B23" s="91" t="n"/>
+      <c r="C23" s="91" t="n"/>
+      <c r="D23" s="95" t="n"/>
+      <c r="E23" s="96" t="n"/>
+      <c r="F23" s="97" t="n"/>
+      <c r="G23" s="96" t="n"/>
+      <c r="H23" s="97" t="n"/>
+      <c r="I23" s="96" t="n"/>
       <c r="J23" s="77">
         <f>IF(G23="","",G23-N(I23))</f>
         <v/>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="98">
         <f>IF(OR(E23="",E23=0,G23=""),"",G23/E23)</f>
         <v/>
       </c>
-      <c r="L23" s="16">
+      <c r="L23" s="98">
         <f>IF(OR(F23="",F23=0,H23=""),"",H23/F23-1)</f>
         <v/>
       </c>
-      <c r="M23" s="8">
+      <c r="M23" s="99">
         <f>IF(OR(G23="",F23="",H23=""),"",G23*(H23-F23))</f>
         <v/>
       </c>
@@ -1497,30 +1553,30 @@
       </c>
     </row>
     <row r="24" ht="22.05" customHeight="1" s="34">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="94" t="n">
         <v>10</v>
       </c>
-      <c r="B24" s="24" t="n"/>
-      <c r="C24" s="24" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="20" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="20" t="n"/>
+      <c r="B24" s="91" t="n"/>
+      <c r="C24" s="91" t="n"/>
+      <c r="D24" s="95" t="n"/>
+      <c r="E24" s="96" t="n"/>
+      <c r="F24" s="97" t="n"/>
+      <c r="G24" s="96" t="n"/>
+      <c r="H24" s="97" t="n"/>
+      <c r="I24" s="96" t="n"/>
       <c r="J24" s="77">
         <f>IF(G24="","",G24-N(I24))</f>
         <v/>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="98">
         <f>IF(OR(E24="",E24=0,G24=""),"",G24/E24)</f>
         <v/>
       </c>
-      <c r="L24" s="16">
+      <c r="L24" s="98">
         <f>IF(OR(F24="",F24=0,H24=""),"",H24/F24-1)</f>
         <v/>
       </c>
-      <c r="M24" s="8">
+      <c r="M24" s="99">
         <f>IF(OR(G24="",F24="",H24=""),"",G24*(H24-F24))</f>
         <v/>
       </c>
@@ -1530,30 +1586,30 @@
       </c>
     </row>
     <row r="25" ht="22.05" customHeight="1" s="34">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="24" t="n"/>
-      <c r="C25" s="24" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="20" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="20" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="20" t="n"/>
+      <c r="B25" s="91" t="n"/>
+      <c r="C25" s="91" t="n"/>
+      <c r="D25" s="95" t="n"/>
+      <c r="E25" s="96" t="n"/>
+      <c r="F25" s="97" t="n"/>
+      <c r="G25" s="96" t="n"/>
+      <c r="H25" s="97" t="n"/>
+      <c r="I25" s="96" t="n"/>
       <c r="J25" s="77">
         <f>IF(G25="","",G25-N(I25))</f>
         <v/>
       </c>
-      <c r="K25" s="16">
+      <c r="K25" s="98">
         <f>IF(OR(E25="",E25=0,G25=""),"",G25/E25)</f>
         <v/>
       </c>
-      <c r="L25" s="16">
+      <c r="L25" s="98">
         <f>IF(OR(F25="",F25=0,H25=""),"",H25/F25-1)</f>
         <v/>
       </c>
-      <c r="M25" s="8">
+      <c r="M25" s="99">
         <f>IF(OR(G25="",F25="",H25=""),"",G25*(H25-F25))</f>
         <v/>
       </c>
@@ -1563,30 +1619,30 @@
       </c>
     </row>
     <row r="26" ht="22.05" customHeight="1" s="34">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="B26" s="24" t="n"/>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="20" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="20" t="n"/>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="20" t="n"/>
+      <c r="B26" s="91" t="n"/>
+      <c r="C26" s="91" t="n"/>
+      <c r="D26" s="95" t="n"/>
+      <c r="E26" s="96" t="n"/>
+      <c r="F26" s="97" t="n"/>
+      <c r="G26" s="96" t="n"/>
+      <c r="H26" s="97" t="n"/>
+      <c r="I26" s="96" t="n"/>
       <c r="J26" s="77">
         <f>IF(G26="","",G26-N(I26))</f>
         <v/>
       </c>
-      <c r="K26" s="16">
+      <c r="K26" s="98">
         <f>IF(OR(E26="",E26=0,G26=""),"",G26/E26)</f>
         <v/>
       </c>
-      <c r="L26" s="16">
+      <c r="L26" s="98">
         <f>IF(OR(F26="",F26=0,H26=""),"",H26/F26-1)</f>
         <v/>
       </c>
-      <c r="M26" s="8">
+      <c r="M26" s="99">
         <f>IF(OR(G26="",F26="",H26=""),"",G26*(H26-F26))</f>
         <v/>
       </c>
@@ -1596,30 +1652,30 @@
       </c>
     </row>
     <row r="27" ht="22.05" customHeight="1" s="34">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="94" t="n">
         <v>13</v>
       </c>
-      <c r="B27" s="24" t="n"/>
-      <c r="C27" s="24" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="20" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="20" t="n"/>
+      <c r="B27" s="91" t="n"/>
+      <c r="C27" s="91" t="n"/>
+      <c r="D27" s="95" t="n"/>
+      <c r="E27" s="96" t="n"/>
+      <c r="F27" s="97" t="n"/>
+      <c r="G27" s="96" t="n"/>
+      <c r="H27" s="97" t="n"/>
+      <c r="I27" s="96" t="n"/>
       <c r="J27" s="77">
         <f>IF(G27="","",G27-N(I27))</f>
         <v/>
       </c>
-      <c r="K27" s="16">
+      <c r="K27" s="98">
         <f>IF(OR(E27="",E27=0,G27=""),"",G27/E27)</f>
         <v/>
       </c>
-      <c r="L27" s="16">
+      <c r="L27" s="98">
         <f>IF(OR(F27="",F27=0,H27=""),"",H27/F27-1)</f>
         <v/>
       </c>
-      <c r="M27" s="8">
+      <c r="M27" s="99">
         <f>IF(OR(G27="",F27="",H27=""),"",G27*(H27-F27))</f>
         <v/>
       </c>
@@ -1629,30 +1685,30 @@
       </c>
     </row>
     <row r="28" ht="22.05" customHeight="1" s="34">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="94" t="n">
         <v>14</v>
       </c>
-      <c r="B28" s="24" t="n"/>
-      <c r="C28" s="24" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="20" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="20" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="20" t="n"/>
+      <c r="B28" s="91" t="n"/>
+      <c r="C28" s="91" t="n"/>
+      <c r="D28" s="95" t="n"/>
+      <c r="E28" s="96" t="n"/>
+      <c r="F28" s="97" t="n"/>
+      <c r="G28" s="96" t="n"/>
+      <c r="H28" s="97" t="n"/>
+      <c r="I28" s="96" t="n"/>
       <c r="J28" s="77">
         <f>IF(G28="","",G28-N(I28))</f>
         <v/>
       </c>
-      <c r="K28" s="16">
+      <c r="K28" s="98">
         <f>IF(OR(E28="",E28=0,G28=""),"",G28/E28)</f>
         <v/>
       </c>
-      <c r="L28" s="16">
+      <c r="L28" s="98">
         <f>IF(OR(F28="",F28=0,H28=""),"",H28/F28-1)</f>
         <v/>
       </c>
-      <c r="M28" s="8">
+      <c r="M28" s="99">
         <f>IF(OR(G28="",F28="",H28=""),"",G28*(H28-F28))</f>
         <v/>
       </c>
@@ -1662,30 +1718,30 @@
       </c>
     </row>
     <row r="29" ht="22.05" customHeight="1" s="34">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="94" t="n">
         <v>15</v>
       </c>
-      <c r="B29" s="24" t="n"/>
-      <c r="C29" s="24" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="20" t="n"/>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="20" t="n"/>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="20" t="n"/>
+      <c r="B29" s="91" t="n"/>
+      <c r="C29" s="91" t="n"/>
+      <c r="D29" s="95" t="n"/>
+      <c r="E29" s="96" t="n"/>
+      <c r="F29" s="97" t="n"/>
+      <c r="G29" s="96" t="n"/>
+      <c r="H29" s="97" t="n"/>
+      <c r="I29" s="96" t="n"/>
       <c r="J29" s="77">
         <f>IF(G29="","",G29-N(I29))</f>
         <v/>
       </c>
-      <c r="K29" s="16">
+      <c r="K29" s="98">
         <f>IF(OR(E29="",E29=0,G29=""),"",G29/E29)</f>
         <v/>
       </c>
-      <c r="L29" s="16">
+      <c r="L29" s="98">
         <f>IF(OR(F29="",F29=0,H29=""),"",H29/F29-1)</f>
         <v/>
       </c>
-      <c r="M29" s="8">
+      <c r="M29" s="99">
         <f>IF(OR(G29="",F29="",H29=""),"",G29*(H29-F29))</f>
         <v/>
       </c>
@@ -1695,30 +1751,30 @@
       </c>
     </row>
     <row r="30" ht="22.05" customHeight="1" s="34">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="94" t="n">
         <v>16</v>
       </c>
-      <c r="B30" s="24" t="n"/>
-      <c r="C30" s="24" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="20" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="20" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="20" t="n"/>
+      <c r="B30" s="91" t="n"/>
+      <c r="C30" s="91" t="n"/>
+      <c r="D30" s="95" t="n"/>
+      <c r="E30" s="96" t="n"/>
+      <c r="F30" s="97" t="n"/>
+      <c r="G30" s="96" t="n"/>
+      <c r="H30" s="97" t="n"/>
+      <c r="I30" s="96" t="n"/>
       <c r="J30" s="77">
         <f>IF(G30="","",G30-N(I30))</f>
         <v/>
       </c>
-      <c r="K30" s="16">
+      <c r="K30" s="98">
         <f>IF(OR(E30="",E30=0,G30=""),"",G30/E30)</f>
         <v/>
       </c>
-      <c r="L30" s="16">
+      <c r="L30" s="98">
         <f>IF(OR(F30="",F30=0,H30=""),"",H30/F30-1)</f>
         <v/>
       </c>
-      <c r="M30" s="8">
+      <c r="M30" s="99">
         <f>IF(OR(G30="",F30="",H30=""),"",G30*(H30-F30))</f>
         <v/>
       </c>
@@ -1728,30 +1784,30 @@
       </c>
     </row>
     <row r="31" ht="22.05" customHeight="1" s="34">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="94" t="n">
         <v>17</v>
       </c>
-      <c r="B31" s="24" t="n"/>
-      <c r="C31" s="24" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="20" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="20" t="n"/>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="20" t="n"/>
+      <c r="B31" s="91" t="n"/>
+      <c r="C31" s="91" t="n"/>
+      <c r="D31" s="95" t="n"/>
+      <c r="E31" s="96" t="n"/>
+      <c r="F31" s="97" t="n"/>
+      <c r="G31" s="96" t="n"/>
+      <c r="H31" s="97" t="n"/>
+      <c r="I31" s="96" t="n"/>
       <c r="J31" s="77">
         <f>IF(G31="","",G31-N(I31))</f>
         <v/>
       </c>
-      <c r="K31" s="16">
+      <c r="K31" s="98">
         <f>IF(OR(E31="",E31=0,G31=""),"",G31/E31)</f>
         <v/>
       </c>
-      <c r="L31" s="16">
+      <c r="L31" s="98">
         <f>IF(OR(F31="",F31=0,H31=""),"",H31/F31-1)</f>
         <v/>
       </c>
-      <c r="M31" s="8">
+      <c r="M31" s="99">
         <f>IF(OR(G31="",F31="",H31=""),"",G31*(H31-F31))</f>
         <v/>
       </c>
@@ -1761,30 +1817,30 @@
       </c>
     </row>
     <row r="32" ht="22.05" customHeight="1" s="34">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="94" t="n">
         <v>18</v>
       </c>
-      <c r="B32" s="24" t="n"/>
-      <c r="C32" s="24" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="20" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="20" t="n"/>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="20" t="n"/>
+      <c r="B32" s="91" t="n"/>
+      <c r="C32" s="91" t="n"/>
+      <c r="D32" s="95" t="n"/>
+      <c r="E32" s="96" t="n"/>
+      <c r="F32" s="97" t="n"/>
+      <c r="G32" s="96" t="n"/>
+      <c r="H32" s="97" t="n"/>
+      <c r="I32" s="96" t="n"/>
       <c r="J32" s="77">
         <f>IF(G32="","",G32-N(I32))</f>
         <v/>
       </c>
-      <c r="K32" s="16">
+      <c r="K32" s="98">
         <f>IF(OR(E32="",E32=0,G32=""),"",G32/E32)</f>
         <v/>
       </c>
-      <c r="L32" s="16">
+      <c r="L32" s="98">
         <f>IF(OR(F32="",F32=0,H32=""),"",H32/F32-1)</f>
         <v/>
       </c>
-      <c r="M32" s="8">
+      <c r="M32" s="99">
         <f>IF(OR(G32="",F32="",H32=""),"",G32*(H32-F32))</f>
         <v/>
       </c>
@@ -1794,30 +1850,30 @@
       </c>
     </row>
     <row r="33" ht="22.05" customHeight="1" s="34">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="94" t="n">
         <v>19</v>
       </c>
-      <c r="B33" s="24" t="n"/>
-      <c r="C33" s="24" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="20" t="n"/>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="20" t="n"/>
-      <c r="H33" s="7" t="n"/>
-      <c r="I33" s="20" t="n"/>
+      <c r="B33" s="91" t="n"/>
+      <c r="C33" s="91" t="n"/>
+      <c r="D33" s="95" t="n"/>
+      <c r="E33" s="96" t="n"/>
+      <c r="F33" s="97" t="n"/>
+      <c r="G33" s="96" t="n"/>
+      <c r="H33" s="97" t="n"/>
+      <c r="I33" s="96" t="n"/>
       <c r="J33" s="77">
         <f>IF(G33="","",G33-N(I33))</f>
         <v/>
       </c>
-      <c r="K33" s="16">
+      <c r="K33" s="98">
         <f>IF(OR(E33="",E33=0,G33=""),"",G33/E33)</f>
         <v/>
       </c>
-      <c r="L33" s="16">
+      <c r="L33" s="98">
         <f>IF(OR(F33="",F33=0,H33=""),"",H33/F33-1)</f>
         <v/>
       </c>
-      <c r="M33" s="8">
+      <c r="M33" s="99">
         <f>IF(OR(G33="",F33="",H33=""),"",G33*(H33-F33))</f>
         <v/>
       </c>
@@ -1827,30 +1883,30 @@
       </c>
     </row>
     <row r="34" ht="22.05" customHeight="1" s="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="94" t="n">
         <v>20</v>
       </c>
-      <c r="B34" s="24" t="n"/>
-      <c r="C34" s="24" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="20" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="20" t="n"/>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="20" t="n"/>
+      <c r="B34" s="91" t="n"/>
+      <c r="C34" s="91" t="n"/>
+      <c r="D34" s="95" t="n"/>
+      <c r="E34" s="96" t="n"/>
+      <c r="F34" s="97" t="n"/>
+      <c r="G34" s="96" t="n"/>
+      <c r="H34" s="97" t="n"/>
+      <c r="I34" s="96" t="n"/>
       <c r="J34" s="77">
         <f>IF(G34="","",G34-N(I34))</f>
         <v/>
       </c>
-      <c r="K34" s="16">
+      <c r="K34" s="98">
         <f>IF(OR(E34="",E34=0,G34=""),"",G34/E34)</f>
         <v/>
       </c>
-      <c r="L34" s="16">
+      <c r="L34" s="98">
         <f>IF(OR(F34="",F34=0,H34=""),"",H34/F34-1)</f>
         <v/>
       </c>
-      <c r="M34" s="8">
+      <c r="M34" s="99">
         <f>IF(OR(G34="",F34="",H34=""),"",G34*(H34-F34))</f>
         <v/>
       </c>
@@ -1876,7 +1932,7 @@
       <c r="J35" s="90" t="n"/>
       <c r="K35" s="90" t="n"/>
       <c r="L35" s="84" t="n"/>
-      <c r="M35" s="86">
+      <c r="M35" s="100">
         <f>SUM(M15:M34)</f>
         <v/>
       </c>
@@ -1903,7 +1959,7 @@
       <c r="M37" s="90" t="n"/>
       <c r="N37" s="84" t="n"/>
     </row>
-    <row r="38" ht="18" customHeight="1" s="34">
+    <row r="38" ht="81" customHeight="1" s="34">
       <c r="A38" s="22" t="inlineStr">
         <is>
           <t>Valor presupuestado de lo comprado</t>
@@ -1912,12 +1968,12 @@
       <c r="B38" s="90" t="n"/>
       <c r="C38" s="90" t="n"/>
       <c r="D38" s="84" t="n"/>
-      <c r="E38" s="41">
+      <c r="E38" s="101">
         <f>SUMPRODUCT(N(+G15:G34),N(+F15:F34))</f>
         <v/>
       </c>
       <c r="F38" s="84" t="n"/>
-      <c r="H38" s="24" t="inlineStr">
+      <c r="H38" s="102" t="inlineStr">
         <is>
           <t>Cómo leer el semáforo (variación de precio):
   OK = el precio real es igual o menor que el presupuestado.
@@ -1942,7 +1998,7 @@
       <c r="B39" s="90" t="n"/>
       <c r="C39" s="90" t="n"/>
       <c r="D39" s="84" t="n"/>
-      <c r="E39" s="41">
+      <c r="E39" s="101">
         <f>SUMPRODUCT(N(+G15:G34),N(+H15:H34))</f>
         <v/>
       </c>
@@ -1959,7 +2015,7 @@
       <c r="B40" s="90" t="n"/>
       <c r="C40" s="90" t="n"/>
       <c r="D40" s="84" t="n"/>
-      <c r="E40" s="41">
+      <c r="E40" s="101">
         <f>E39-E38</f>
         <v/>
       </c>
@@ -1976,7 +2032,7 @@
       <c r="B41" s="90" t="n"/>
       <c r="C41" s="90" t="n"/>
       <c r="D41" s="84" t="n"/>
-      <c r="E41" s="80">
+      <c r="E41" s="103">
         <f>IF(E38=0,"",E39/E38-1)</f>
         <v/>
       </c>
@@ -2042,10 +2098,10 @@
       </c>
       <c r="B45" s="90" t="n"/>
       <c r="C45" s="84" t="n"/>
-      <c r="D45" s="24" t="n"/>
-      <c r="E45" s="90" t="n"/>
-      <c r="F45" s="90" t="n"/>
-      <c r="G45" s="84" t="n"/>
+      <c r="D45" s="91" t="n"/>
+      <c r="E45" s="92" t="n"/>
+      <c r="F45" s="92" t="n"/>
+      <c r="G45" s="93" t="n"/>
       <c r="H45" s="22" t="inlineStr">
         <is>
           <t>Firma:</t>
@@ -2053,10 +2109,10 @@
       </c>
       <c r="I45" s="90" t="n"/>
       <c r="J45" s="84" t="n"/>
-      <c r="K45" s="24" t="n"/>
-      <c r="L45" s="90" t="n"/>
-      <c r="M45" s="90" t="n"/>
-      <c r="N45" s="84" t="n"/>
+      <c r="K45" s="91" t="n"/>
+      <c r="L45" s="92" t="n"/>
+      <c r="M45" s="92" t="n"/>
+      <c r="N45" s="93" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1" s="34">
       <c r="A46" s="22" t="inlineStr">
@@ -2066,10 +2122,10 @@
       </c>
       <c r="B46" s="90" t="n"/>
       <c r="C46" s="84" t="n"/>
-      <c r="D46" s="24" t="n"/>
-      <c r="E46" s="90" t="n"/>
-      <c r="F46" s="90" t="n"/>
-      <c r="G46" s="84" t="n"/>
+      <c r="D46" s="91" t="n"/>
+      <c r="E46" s="92" t="n"/>
+      <c r="F46" s="92" t="n"/>
+      <c r="G46" s="93" t="n"/>
       <c r="H46" s="22" t="inlineStr">
         <is>
           <t>Nombre:</t>
@@ -2077,10 +2133,10 @@
       </c>
       <c r="I46" s="90" t="n"/>
       <c r="J46" s="84" t="n"/>
-      <c r="K46" s="24" t="n"/>
-      <c r="L46" s="90" t="n"/>
-      <c r="M46" s="90" t="n"/>
-      <c r="N46" s="84" t="n"/>
+      <c r="K46" s="91" t="n"/>
+      <c r="L46" s="92" t="n"/>
+      <c r="M46" s="92" t="n"/>
+      <c r="N46" s="93" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1" s="34">
       <c r="A47" s="22" t="inlineStr">
@@ -2090,10 +2146,10 @@
       </c>
       <c r="B47" s="90" t="n"/>
       <c r="C47" s="84" t="n"/>
-      <c r="D47" s="24" t="n"/>
-      <c r="E47" s="90" t="n"/>
-      <c r="F47" s="90" t="n"/>
-      <c r="G47" s="84" t="n"/>
+      <c r="D47" s="91" t="n"/>
+      <c r="E47" s="92" t="n"/>
+      <c r="F47" s="92" t="n"/>
+      <c r="G47" s="93" t="n"/>
       <c r="H47" s="22" t="inlineStr">
         <is>
           <t>Cargo:</t>
@@ -2101,12 +2157,13 @@
       </c>
       <c r="I47" s="90" t="n"/>
       <c r="J47" s="84" t="n"/>
-      <c r="K47" s="24" t="n"/>
-      <c r="L47" s="90" t="n"/>
-      <c r="M47" s="90" t="n"/>
-      <c r="N47" s="84" t="n"/>
+      <c r="K47" s="91" t="n"/>
+      <c r="L47" s="92" t="n"/>
+      <c r="M47" s="92" t="n"/>
+      <c r="N47" s="93" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="54">
     <mergeCell ref="A9:N9"/>
     <mergeCell ref="H46:J46"/>
